--- a/LSix/LSIX_Prioridad_y_Mangos_Bajitos.xlsx
+++ b/LSix/LSIX_Prioridad_y_Mangos_Bajitos.xlsx
@@ -10,9 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como_se_priorizo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mangos_Bajitos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AeroMexico_Inbursa" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mundomex" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_Sep_Dic" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking_Sep_Dic" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_Sep_Dic" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking_Sep_Dic" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1611,204 +1610,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Mundomex — análisis de fit</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Grupo Mundomex, mundomex.com.mx · agencia de viajes con 50+ años · oficinas en Polanco · revisado 24-ago-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>QUÉ SON</t>
-        </is>
-      </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>Cinco líneas de negocio: Grupos y Convenciones · Viajes de Placer · Eventos Deportivos (On Location Experiences y Paddock Club — o sea F1) · Viajes de Lujo · Servicios Empresariales.</t>
-        </is>
-      </c>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="28" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>SU CARTERA DE CLIENTES</t>
-        </is>
-      </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Zurich, Hyundai, Mars, Mazda, Toyota, Coca-Cola, Ford, Cisco… y GRISI. Cartera corporativa de primer nivel — y una conexión cruzada interesante con otro target del pipeline.</t>
-        </is>
-      </c>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>EL HALLAZGO ESTRUCTURAL</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>NO tienen eCommerce transaccional. El sitio corre en Drupal 10, sin carrito ni motor de reservas: cada paquete termina en un botón que manda a WhatsApp (55 3686 2988) o a formulario de contacto. Stack ligero: GTM (GTM-WLQ77WS) y verificación de dominio de Facebook.</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="28" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>QUÉ SIGNIFICA PARA EL MODELO</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>Sin transacción online no hay 'venta confirmada y atribuida'. El evento de conversión tendría que ser un LEAD CALIFICADO — solicitud de cotización con datos completos — no una venta. Es CPL, no CPA puro.</t>
-        </is>
-      </c>
-      <c r="C7" s="30" t="n"/>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="28" t="inlineStr">
-        <is>
-          <t>ANÁLISIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>POR QUÉ AUN ASÍ ES BUEN MANGO</t>
-        </is>
-      </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>Ticket altísimo: un viaje de lujo o un paquete de Paddock Club vale decenas de miles de pesos. Un lead calificado en esa categoría tiene un valor enorme, y hoy probablemente lo compran a CPC o por referido sin medición.</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="n"/>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="28" t="inlineStr">
-        <is>
-          <t>ANÁLISIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>EL GANCHO DE TEMPORADA</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>Eventos Deportivos con On Location y Paddock Club. El Gran Premio de México cae en la ventana de octubre — justo en el trimestre que estamos planeando. [VERIFICAR fecha exacta 2026]</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>ANÁLISIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>LA CONVERSACIÓN CORRECTA</t>
-        </is>
-      </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>No llegar con CPA de eCommerce. Llegar con: '¿cuánto te cuesta hoy un lead de un viaje de lujo, y cuántos de esos cierran?' De ahí sale si el modelo aplica y a qué precio.</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="n"/>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="28" t="inlineStr">
-        <is>
-          <t>RECOMENDACIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>RIESGO A CUIDAR</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>Es amigo del CEO. Igual que con Grisi: si el producto no encaja, la conversación exploratoria protege la relación mejor que un pitch forzado.</t>
-        </is>
-      </c>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="28" t="inlineStr">
-        <is>
-          <t>RECOMENDACIÓN</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B6:D6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2007,13 +1808,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2568,37 +2369,37 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Mundomex</t>
+          <t>Innovasport</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Deportes</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Amigo del CEO</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Drupal, sin checkout</t>
+          <t>~2K Google · 29 variantes Meta</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Lead calificado (CPL)</t>
+          <t>Venta en app</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>ALTA · CPL</t>
+          <t>ALTA · el mejor fit técnico</t>
         </is>
       </c>
     </row>
@@ -2608,17 +2409,17 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Innovasport</t>
+          <t>El Palacio de Hierro</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Deportes</t>
+          <t>Departamental</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -2628,17 +2429,17 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>~2K Google · 29 variantes Meta</t>
+          <t>Soicos instalado · ~1.300 Meta</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Venta en app</t>
+          <t>% sobre revenue</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>ALTA · el mejor fit técnico</t>
+          <t>ALTA</t>
         </is>
       </c>
     </row>
@@ -2648,32 +2449,32 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>El Palacio de Hierro</t>
+          <t>Elektra / Baz</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Departamental</t>
+          <t>Departamental + fintech</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Soicos instalado · ~1.300 Meta</t>
+          <t>~9K Google · ~21 Meta propios</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>% sobre revenue</t>
+          <t>Venta en app / originación</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -2688,37 +2489,37 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Elektra / Baz</t>
+          <t>L'Oréal México (FRABEL)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Departamental + fintech</t>
+          <t>CPG / motor 2</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Sin relación</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>~9K Google · ~21 Meta propios</t>
+          <t>~702 Meta · pauta a 3 retailers</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Venta en app / originación</t>
+          <t>Venta en ficha de retailer</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>ALTA · motor 2</t>
         </is>
       </c>
     </row>
@@ -2728,37 +2529,37 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>L'Oréal México (FRABEL)</t>
+          <t>Samsung México</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>CPG / motor 2</t>
+          <t>Electrónica</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Sin relación</t>
+          <t>Conocido — co-jurado</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>~702 Meta · pauta a 3 retailers</t>
+          <t>CPA premiado USD 9.4M</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Venta en ficha de retailer</t>
+          <t>Venta en eStore / retailer</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>ALTA · motor 2</t>
+          <t>ALTA · ciclo 4–6 meses</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2569,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Samsung México</t>
+          <t>Sodimac México</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Electrónica</t>
+          <t>Hogar</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -2783,22 +2584,22 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Conocido — co-jurado</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>CPA premiado USD 9.4M</t>
+          <t>RTB House · Criteo · Awin · AppsFlyer</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Venta en eStore / retailer</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>ALTA · ciclo 4–6 meses</t>
+          <t>Venta en app</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
     </row>
@@ -2808,17 +2609,17 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Sodimac México</t>
+          <t>Volaris</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Hogar</t>
+          <t>Aerolínea</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -2828,12 +2629,12 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>RTB House · Criteo · Awin · AppsFlyer</t>
+          <t>~5K Google · solo 5 multivariante</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Venta en app</t>
+          <t>Boleto emitido</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -2848,12 +2649,12 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Volaris</t>
+          <t>Kueski Pay</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Aerolínea</t>
+          <t>BNPL</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -2868,12 +2669,12 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>~5K Google · solo 5 multivariante</t>
+          <t>~400 Google · ~99 Meta</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Boleto emitido</t>
+          <t>Evento de originación</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
@@ -2888,17 +2689,17 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Kueski Pay</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>BNPL</t>
+          <t>Departamental</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -2908,55 +2709,15 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>~400 Google · ~99 Meta</t>
+          <t>~20k dominio · ~2.200 Meta</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Evento de originación</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Departamental</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>~20k dominio · ~2.200 Meta</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
           <t>Venta en app o motor 2</t>
         </is>
       </c>
-      <c r="H26" s="15" t="inlineStr">
+      <c r="H25" s="15" t="inlineStr">
         <is>
           <t>SIEMBRA</t>
         </is>
